--- a/横版过关地图.xlsx
+++ b/横版过关地图.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitHub\ECE3200-Final-Project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0646B730-CABE-44DB-B89E-0C3969A9FD64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5B86FC0-4A1A-4DE2-B515-352B9DA351F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="城堡外" sheetId="1" r:id="rId1"/>
@@ -569,82 +569,82 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="D1:BC87"/>
+  <dimension ref="D1:AS87"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="66" width="5.58203125" customWidth="1"/>
+    <col min="1" max="56" width="5.58203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="4:55" ht="33.5" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="4:55" ht="33.5" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="3" spans="4:55" ht="33.5" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="4" spans="4:55" ht="33.5" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="5" spans="4:55" ht="33.5" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="6" spans="4:55" ht="33.5" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="7" spans="4:55" ht="33.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="AL7" s="6" t="s">
+    <row r="1" spans="4:45" ht="33.5" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="4:45" ht="33.5" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="3" spans="4:45" ht="33.5" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="4" spans="4:45" ht="33.5" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="5" spans="4:45" ht="33.5" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="6" spans="4:45" ht="33.5" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="7" spans="4:45" ht="33.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="AD7" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="AM7" s="6"/>
-      <c r="AN7" s="6"/>
-      <c r="AO7" s="6"/>
-      <c r="AP7" s="6"/>
-    </row>
-    <row r="8" spans="4:55" ht="33.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="AL8" s="2"/>
-      <c r="AM8" s="6" t="s">
+      <c r="AE7" s="6"/>
+      <c r="AF7" s="6"/>
+      <c r="AG7" s="6"/>
+      <c r="AH7" s="6"/>
+    </row>
+    <row r="8" spans="4:45" ht="33.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="AD8" s="2"/>
+      <c r="AE8" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="AN8" s="6"/>
-      <c r="AO8" s="6"/>
-      <c r="AP8" s="6"/>
-    </row>
-    <row r="9" spans="4:55" ht="33.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="AL9" s="3"/>
-      <c r="AM9" s="6" t="s">
+      <c r="AF8" s="6"/>
+      <c r="AG8" s="6"/>
+      <c r="AH8" s="6"/>
+    </row>
+    <row r="9" spans="4:45" ht="33.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="AD9" s="3"/>
+      <c r="AE9" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="AN9" s="6"/>
-      <c r="AO9" s="6"/>
-      <c r="AP9" s="6"/>
-    </row>
-    <row r="10" spans="4:55" ht="33.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="AL10" s="7"/>
-      <c r="AM10" s="6" t="s">
+      <c r="AF9" s="6"/>
+      <c r="AG9" s="6"/>
+      <c r="AH9" s="6"/>
+    </row>
+    <row r="10" spans="4:45" ht="33.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="AD10" s="7"/>
+      <c r="AE10" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="AN10" s="6"/>
-      <c r="AO10" s="6"/>
-      <c r="AP10" s="6"/>
-    </row>
-    <row r="11" spans="4:55" ht="33.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="AL11" s="4"/>
-      <c r="AM11" s="6" t="s">
+      <c r="AF10" s="6"/>
+      <c r="AG10" s="6"/>
+      <c r="AH10" s="6"/>
+    </row>
+    <row r="11" spans="4:45" ht="33.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="AD11" s="4"/>
+      <c r="AE11" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="AN11" s="6"/>
-      <c r="AO11" s="6"/>
-      <c r="AP11" s="6"/>
-    </row>
-    <row r="12" spans="4:55" ht="33.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="AL12" s="5"/>
-      <c r="AM12" s="6" t="s">
+      <c r="AF11" s="6"/>
+      <c r="AG11" s="6"/>
+      <c r="AH11" s="6"/>
+    </row>
+    <row r="12" spans="4:45" ht="33.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="AD12" s="5"/>
+      <c r="AE12" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="AN12" s="6"/>
-      <c r="AO12" s="6"/>
-      <c r="AP12" s="6"/>
-    </row>
-    <row r="13" spans="4:55" ht="33.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="AL13" s="8"/>
-      <c r="AM13" s="6" t="s">
+      <c r="AF12" s="6"/>
+      <c r="AG12" s="6"/>
+      <c r="AH12" s="6"/>
+    </row>
+    <row r="13" spans="4:45" ht="33.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="AD13" s="8"/>
+      <c r="AE13" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="AN13" s="6"/>
-      <c r="AO13" s="6"/>
-      <c r="AP13" s="6"/>
-    </row>
-    <row r="14" spans="4:55" ht="33.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AF13" s="6"/>
+      <c r="AG13" s="6"/>
+      <c r="AH13" s="6"/>
+    </row>
+    <row r="14" spans="4:45" ht="33.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D14" s="1"/>
       <c r="E14" s="1"/>
       <c r="F14" s="1"/>
@@ -687,18 +687,8 @@
       <c r="AQ14" s="1"/>
       <c r="AR14" s="1"/>
       <c r="AS14" s="1"/>
-      <c r="AT14" s="1"/>
-      <c r="AU14" s="1"/>
-      <c r="AV14" s="1"/>
-      <c r="AW14" s="1"/>
-      <c r="AX14" s="1"/>
-      <c r="AY14" s="1"/>
-      <c r="AZ14" s="1"/>
-      <c r="BA14" s="1"/>
-      <c r="BB14" s="1"/>
-      <c r="BC14" s="1"/>
-    </row>
-    <row r="15" spans="4:55" ht="33.5" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="15" spans="4:45" ht="33.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D15" s="1"/>
       <c r="E15" s="1"/>
       <c r="F15" s="1"/>
@@ -741,18 +731,8 @@
       <c r="AQ15" s="1"/>
       <c r="AR15" s="1"/>
       <c r="AS15" s="1"/>
-      <c r="AT15" s="1"/>
-      <c r="AU15" s="1"/>
-      <c r="AV15" s="1"/>
-      <c r="AW15" s="1"/>
-      <c r="AX15" s="1"/>
-      <c r="AY15" s="1"/>
-      <c r="AZ15" s="1"/>
-      <c r="BA15" s="1"/>
-      <c r="BB15" s="1"/>
-      <c r="BC15" s="1"/>
-    </row>
-    <row r="16" spans="4:55" ht="33.5" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="16" spans="4:45" ht="33.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D16" s="1"/>
       <c r="E16" s="1"/>
       <c r="F16" s="1"/>
@@ -795,18 +775,8 @@
       <c r="AQ16" s="1"/>
       <c r="AR16" s="1"/>
       <c r="AS16" s="1"/>
-      <c r="AT16" s="1"/>
-      <c r="AU16" s="1"/>
-      <c r="AV16" s="1"/>
-      <c r="AW16" s="1"/>
-      <c r="AX16" s="1"/>
-      <c r="AY16" s="1"/>
-      <c r="AZ16" s="1"/>
-      <c r="BA16" s="1"/>
-      <c r="BB16" s="1"/>
-      <c r="BC16" s="1"/>
-    </row>
-    <row r="17" spans="4:55" ht="33.5" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="17" spans="4:45" ht="33.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D17" s="1"/>
       <c r="E17" s="1"/>
       <c r="F17" s="1"/>
@@ -849,18 +819,8 @@
       <c r="AQ17" s="1"/>
       <c r="AR17" s="1"/>
       <c r="AS17" s="1"/>
-      <c r="AT17" s="1"/>
-      <c r="AU17" s="1"/>
-      <c r="AV17" s="1"/>
-      <c r="AW17" s="1"/>
-      <c r="AX17" s="1"/>
-      <c r="AY17" s="1"/>
-      <c r="AZ17" s="1"/>
-      <c r="BA17" s="1"/>
-      <c r="BB17" s="1"/>
-      <c r="BC17" s="1"/>
-    </row>
-    <row r="18" spans="4:55" ht="33.5" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="18" spans="4:45" ht="33.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D18" s="1"/>
       <c r="E18" s="1"/>
       <c r="F18" s="1"/>
@@ -889,32 +849,22 @@
       <c r="AC18" s="1"/>
       <c r="AD18" s="1"/>
       <c r="AE18" s="1"/>
-      <c r="AF18" s="1"/>
+      <c r="AF18" s="2"/>
       <c r="AG18" s="1"/>
-      <c r="AH18" s="1"/>
-      <c r="AI18" s="1"/>
+      <c r="AH18" s="2"/>
+      <c r="AI18" s="2"/>
       <c r="AJ18" s="1"/>
       <c r="AK18" s="1"/>
       <c r="AL18" s="1"/>
       <c r="AM18" s="1"/>
-      <c r="AN18" s="2"/>
+      <c r="AN18" s="1"/>
       <c r="AO18" s="1"/>
-      <c r="AP18" s="2"/>
-      <c r="AQ18" s="2"/>
+      <c r="AP18" s="1"/>
+      <c r="AQ18" s="1"/>
       <c r="AR18" s="1"/>
-      <c r="AS18" s="2"/>
-      <c r="AT18" s="1"/>
-      <c r="AU18" s="1"/>
-      <c r="AV18" s="1"/>
-      <c r="AW18" s="1"/>
-      <c r="AX18" s="1"/>
-      <c r="AY18" s="1"/>
-      <c r="AZ18" s="1"/>
-      <c r="BA18" s="1"/>
-      <c r="BB18" s="1"/>
-      <c r="BC18" s="5"/>
-    </row>
-    <row r="19" spans="4:55" ht="33.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="AS18" s="5"/>
+    </row>
+    <row r="19" spans="4:45" ht="33.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="D19" s="1"/>
       <c r="E19" s="3"/>
       <c r="F19" s="1"/>
@@ -932,14 +882,14 @@
       <c r="R19" s="1"/>
       <c r="S19" s="1"/>
       <c r="T19" s="1"/>
-      <c r="U19" s="1"/>
+      <c r="U19" s="8"/>
       <c r="V19" s="1"/>
       <c r="W19" s="1"/>
       <c r="X19" s="1"/>
       <c r="Y19" s="1"/>
       <c r="Z19" s="1"/>
       <c r="AA19" s="1"/>
-      <c r="AB19" s="8"/>
+      <c r="AB19" s="1"/>
       <c r="AC19" s="1"/>
       <c r="AD19" s="1"/>
       <c r="AE19" s="1"/>
@@ -956,19 +906,9 @@
       <c r="AP19" s="1"/>
       <c r="AQ19" s="1"/>
       <c r="AR19" s="1"/>
-      <c r="AS19" s="1"/>
-      <c r="AT19" s="1"/>
-      <c r="AU19" s="1"/>
-      <c r="AV19" s="1"/>
-      <c r="AW19" s="1"/>
-      <c r="AX19" s="1"/>
-      <c r="AY19" s="1"/>
-      <c r="AZ19" s="1"/>
-      <c r="BA19" s="1"/>
-      <c r="BB19" s="1"/>
-      <c r="BC19" s="5"/>
-    </row>
-    <row r="20" spans="4:55" ht="33.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AS19" s="5"/>
+    </row>
+    <row r="20" spans="4:45" ht="33.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D20" s="2"/>
       <c r="E20" s="2"/>
       <c r="F20" s="2"/>
@@ -988,41 +928,31 @@
       <c r="T20" s="2"/>
       <c r="U20" s="2"/>
       <c r="V20" s="2"/>
-      <c r="W20" s="7"/>
-      <c r="X20" s="7"/>
+      <c r="W20" s="2"/>
+      <c r="X20" s="2"/>
       <c r="Y20" s="7"/>
       <c r="Z20" s="2"/>
       <c r="AA20" s="2"/>
-      <c r="AB20" s="2"/>
-      <c r="AC20" s="2"/>
+      <c r="AB20" s="7"/>
+      <c r="AC20" s="7"/>
       <c r="AD20" s="2"/>
       <c r="AE20" s="2"/>
       <c r="AF20" s="7"/>
-      <c r="AG20" s="2"/>
+      <c r="AG20" s="7"/>
       <c r="AH20" s="7"/>
-      <c r="AI20" s="2"/>
+      <c r="AI20" s="7"/>
       <c r="AJ20" s="7"/>
-      <c r="AK20" s="7"/>
+      <c r="AK20" s="2"/>
       <c r="AL20" s="2"/>
       <c r="AM20" s="2"/>
-      <c r="AN20" s="7"/>
-      <c r="AO20" s="7"/>
-      <c r="AP20" s="7"/>
-      <c r="AQ20" s="7"/>
-      <c r="AR20" s="7"/>
-      <c r="AS20" s="7"/>
-      <c r="AT20" s="7"/>
-      <c r="AU20" s="2"/>
-      <c r="AV20" s="2"/>
-      <c r="AW20" s="2"/>
-      <c r="AX20" s="2"/>
-      <c r="AY20" s="2"/>
-      <c r="AZ20" s="2"/>
-      <c r="BA20" s="2"/>
-      <c r="BB20" s="2"/>
-      <c r="BC20" s="2"/>
-    </row>
-    <row r="21" spans="4:55" ht="33.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AN20" s="2"/>
+      <c r="AO20" s="2"/>
+      <c r="AP20" s="2"/>
+      <c r="AQ20" s="2"/>
+      <c r="AR20" s="2"/>
+      <c r="AS20" s="2"/>
+    </row>
+    <row r="21" spans="4:45" ht="33.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D21" s="2"/>
       <c r="E21" s="2"/>
       <c r="F21" s="2"/>
@@ -1042,41 +972,31 @@
       <c r="T21" s="2"/>
       <c r="U21" s="2"/>
       <c r="V21" s="2"/>
-      <c r="W21" s="4"/>
-      <c r="X21" s="4"/>
+      <c r="W21" s="2"/>
+      <c r="X21" s="2"/>
       <c r="Y21" s="4"/>
       <c r="Z21" s="2"/>
       <c r="AA21" s="2"/>
-      <c r="AB21" s="2"/>
-      <c r="AC21" s="2"/>
+      <c r="AB21" s="4"/>
+      <c r="AC21" s="4"/>
       <c r="AD21" s="2"/>
       <c r="AE21" s="2"/>
       <c r="AF21" s="4"/>
-      <c r="AG21" s="2"/>
+      <c r="AG21" s="4"/>
       <c r="AH21" s="4"/>
-      <c r="AI21" s="2"/>
+      <c r="AI21" s="4"/>
       <c r="AJ21" s="4"/>
-      <c r="AK21" s="4"/>
+      <c r="AK21" s="2"/>
       <c r="AL21" s="2"/>
       <c r="AM21" s="2"/>
-      <c r="AN21" s="4"/>
-      <c r="AO21" s="4"/>
-      <c r="AP21" s="4"/>
-      <c r="AQ21" s="4"/>
-      <c r="AR21" s="4"/>
-      <c r="AS21" s="4"/>
-      <c r="AT21" s="4"/>
-      <c r="AU21" s="2"/>
-      <c r="AV21" s="2"/>
-      <c r="AW21" s="2"/>
-      <c r="AX21" s="2"/>
-      <c r="AY21" s="2"/>
-      <c r="AZ21" s="2"/>
-      <c r="BA21" s="2"/>
-      <c r="BB21" s="2"/>
-      <c r="BC21" s="2"/>
-    </row>
-    <row r="22" spans="4:55" ht="33.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AN21" s="2"/>
+      <c r="AO21" s="2"/>
+      <c r="AP21" s="2"/>
+      <c r="AQ21" s="2"/>
+      <c r="AR21" s="2"/>
+      <c r="AS21" s="2"/>
+    </row>
+    <row r="22" spans="4:45" ht="33.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D22" s="2"/>
       <c r="E22" s="2"/>
       <c r="F22" s="2"/>
@@ -1119,27 +1039,17 @@
       <c r="AQ22" s="2"/>
       <c r="AR22" s="2"/>
       <c r="AS22" s="2"/>
-      <c r="AT22" s="2"/>
-      <c r="AU22" s="2"/>
-      <c r="AV22" s="2"/>
-      <c r="AW22" s="2"/>
-      <c r="AX22" s="2"/>
-      <c r="AY22" s="2"/>
-      <c r="AZ22" s="2"/>
-      <c r="BA22" s="2"/>
-      <c r="BB22" s="2"/>
-      <c r="BC22" s="2"/>
-    </row>
-    <row r="23" spans="4:55" ht="33.5" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="24" spans="4:55" ht="33.5" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="25" spans="4:55" ht="33.5" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="26" spans="4:55" ht="33.5" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="27" spans="4:55" ht="33.5" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="28" spans="4:55" ht="33.5" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="29" spans="4:55" ht="33.5" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="30" spans="4:55" ht="33.5" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="31" spans="4:55" ht="33.5" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="32" spans="4:55" ht="33.5" customHeight="1" x14ac:dyDescent="0.3"/>
+    </row>
+    <row r="23" spans="4:45" ht="33.5" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="24" spans="4:45" ht="33.5" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="25" spans="4:45" ht="33.5" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="26" spans="4:45" ht="33.5" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="27" spans="4:45" ht="33.5" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="28" spans="4:45" ht="33.5" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="29" spans="4:45" ht="33.5" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="30" spans="4:45" ht="33.5" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="31" spans="4:45" ht="33.5" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="32" spans="4:45" ht="33.5" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="33" ht="33.5" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="34" ht="33.5" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="35" ht="33.5" customHeight="1" x14ac:dyDescent="0.3"/>
@@ -1203,19 +1113,19 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2A1CA41B-56F1-42DF-B2F4-601862D20F90}">
-  <dimension ref="D1:BC87"/>
+  <dimension ref="D1:AT87"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="66" width="5.58203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="4:55" ht="33.5" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="4:55" ht="33.5" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="3" spans="4:55" ht="33.5" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="4" spans="4:55" ht="33.5" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="5" spans="4:55" ht="33.5" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="6" spans="4:55" ht="33.5" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="7" spans="4:55" ht="33.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="4:46" ht="33.5" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="4:46" ht="33.5" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="3" spans="4:46" ht="33.5" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="4" spans="4:46" ht="33.5" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="5" spans="4:46" ht="33.5" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="6" spans="4:46" ht="33.5" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="7" spans="4:46" ht="33.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="AL7" s="6" t="s">
         <v>10</v>
       </c>
@@ -1224,7 +1134,7 @@
       <c r="AO7" s="6"/>
       <c r="AP7" s="6"/>
     </row>
-    <row r="8" spans="4:55" ht="33.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="4:46" ht="33.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="AL8" s="2"/>
       <c r="AM8" s="6" t="s">
         <v>1</v>
@@ -1233,7 +1143,7 @@
       <c r="AO8" s="6"/>
       <c r="AP8" s="6"/>
     </row>
-    <row r="9" spans="4:55" ht="33.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="4:46" ht="33.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="AL9" s="3"/>
       <c r="AM9" s="6" t="s">
         <v>2</v>
@@ -1242,7 +1152,7 @@
       <c r="AO9" s="6"/>
       <c r="AP9" s="6"/>
     </row>
-    <row r="10" spans="4:55" ht="33.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="4:46" ht="33.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="AL10" s="7"/>
       <c r="AM10" s="6" t="s">
         <v>3</v>
@@ -1251,7 +1161,7 @@
       <c r="AO10" s="6"/>
       <c r="AP10" s="6"/>
     </row>
-    <row r="11" spans="4:55" ht="33.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="11" spans="4:46" ht="33.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="AL11" s="4"/>
       <c r="AM11" s="6" t="s">
         <v>4</v>
@@ -1260,7 +1170,7 @@
       <c r="AO11" s="6"/>
       <c r="AP11" s="6"/>
     </row>
-    <row r="12" spans="4:55" ht="33.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="12" spans="4:46" ht="33.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="AL12" s="5"/>
       <c r="AM12" s="6" t="s">
         <v>5</v>
@@ -1269,7 +1179,7 @@
       <c r="AO12" s="6"/>
       <c r="AP12" s="6"/>
     </row>
-    <row r="13" spans="4:55" ht="33.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="13" spans="4:46" ht="33.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="AL13" s="8"/>
       <c r="AM13" s="6" t="s">
         <v>7</v>
@@ -1278,7 +1188,7 @@
       <c r="AO13" s="6"/>
       <c r="AP13" s="6"/>
     </row>
-    <row r="14" spans="4:55" ht="33.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="14" spans="4:46" ht="33.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="AL14" s="9"/>
       <c r="AM14" s="6" t="s">
         <v>8</v>
@@ -1291,7 +1201,7 @@
       <c r="AS14" s="6"/>
       <c r="AT14" s="6"/>
     </row>
-    <row r="15" spans="4:55" ht="33.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="15" spans="4:46" ht="33.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="AL15" s="11"/>
       <c r="AM15" s="6" t="s">
         <v>12</v>
@@ -1304,7 +1214,7 @@
       <c r="AS15" s="6"/>
       <c r="AT15" s="6"/>
     </row>
-    <row r="16" spans="4:55" ht="33.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="4:46" ht="33.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D16" s="1"/>
       <c r="E16" s="1"/>
       <c r="F16" s="1"/>
@@ -1347,18 +1257,8 @@
       <c r="AQ16" s="1"/>
       <c r="AR16" s="1"/>
       <c r="AS16" s="1"/>
-      <c r="AT16" s="1"/>
-      <c r="AU16" s="1"/>
-      <c r="AV16" s="1"/>
-      <c r="AW16" s="1"/>
-      <c r="AX16" s="1"/>
-      <c r="AY16" s="1"/>
-      <c r="AZ16" s="1"/>
-      <c r="BA16" s="1"/>
-      <c r="BB16" s="1"/>
-      <c r="BC16" s="1"/>
-    </row>
-    <row r="17" spans="4:55" ht="33.5" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="17" spans="4:45" ht="33.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D17" s="1"/>
       <c r="E17" s="1"/>
       <c r="F17" s="1"/>
@@ -1401,18 +1301,8 @@
       <c r="AQ17" s="1"/>
       <c r="AR17" s="1"/>
       <c r="AS17" s="1"/>
-      <c r="AT17" s="1"/>
-      <c r="AU17" s="1"/>
-      <c r="AV17" s="1"/>
-      <c r="AW17" s="1"/>
-      <c r="AX17" s="1"/>
-      <c r="AY17" s="1"/>
-      <c r="AZ17" s="1"/>
-      <c r="BA17" s="1"/>
-      <c r="BB17" s="1"/>
-      <c r="BC17" s="1"/>
-    </row>
-    <row r="18" spans="4:55" ht="33.5" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="18" spans="4:45" ht="33.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D18" s="1"/>
       <c r="E18" s="1"/>
       <c r="F18" s="1"/>
@@ -1438,8 +1328,8 @@
       <c r="Z18" s="1"/>
       <c r="AA18" s="1"/>
       <c r="AB18" s="1"/>
-      <c r="AC18" s="1"/>
-      <c r="AD18" s="9"/>
+      <c r="AC18" s="9"/>
+      <c r="AD18" s="1"/>
       <c r="AE18" s="1"/>
       <c r="AF18" s="1"/>
       <c r="AG18" s="1"/>
@@ -1455,18 +1345,8 @@
       <c r="AQ18" s="1"/>
       <c r="AR18" s="1"/>
       <c r="AS18" s="1"/>
-      <c r="AT18" s="1"/>
-      <c r="AU18" s="1"/>
-      <c r="AV18" s="1"/>
-      <c r="AW18" s="1"/>
-      <c r="AX18" s="1"/>
-      <c r="AY18" s="1"/>
-      <c r="AZ18" s="1"/>
-      <c r="BA18" s="1"/>
-      <c r="BB18" s="1"/>
-      <c r="BC18" s="1"/>
-    </row>
-    <row r="19" spans="4:55" ht="33.5" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="19" spans="4:45" ht="33.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D19" s="1"/>
       <c r="E19" s="1"/>
       <c r="F19" s="1"/>
@@ -1487,22 +1367,22 @@
       <c r="U19" s="1"/>
       <c r="V19" s="1"/>
       <c r="W19" s="1"/>
-      <c r="X19" s="1"/>
-      <c r="Y19" s="11"/>
+      <c r="X19" s="11"/>
+      <c r="Y19" s="1"/>
       <c r="Z19" s="1"/>
       <c r="AA19" s="1"/>
       <c r="AB19" s="1"/>
-      <c r="AC19" s="1"/>
-      <c r="AD19" s="10" t="s">
+      <c r="AC19" s="10" t="s">
         <v>9</v>
       </c>
+      <c r="AD19" s="1"/>
       <c r="AE19" s="1"/>
       <c r="AF19" s="1"/>
       <c r="AG19" s="1"/>
       <c r="AH19" s="1"/>
       <c r="AI19" s="1"/>
-      <c r="AJ19" s="1"/>
-      <c r="AK19" s="11"/>
+      <c r="AJ19" s="11"/>
+      <c r="AK19" s="1"/>
       <c r="AL19" s="1"/>
       <c r="AM19" s="1"/>
       <c r="AN19" s="1"/>
@@ -1511,18 +1391,8 @@
       <c r="AQ19" s="1"/>
       <c r="AR19" s="1"/>
       <c r="AS19" s="1"/>
-      <c r="AT19" s="1"/>
-      <c r="AU19" s="1"/>
-      <c r="AV19" s="1"/>
-      <c r="AW19" s="1"/>
-      <c r="AX19" s="1"/>
-      <c r="AY19" s="1"/>
-      <c r="AZ19" s="1"/>
-      <c r="BA19" s="1"/>
-      <c r="BB19" s="1"/>
-      <c r="BC19" s="1"/>
-    </row>
-    <row r="20" spans="4:55" ht="33.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="20" spans="4:45" ht="33.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="D20" s="1"/>
       <c r="E20" s="1"/>
       <c r="F20" s="1"/>
@@ -1535,17 +1405,17 @@
       <c r="M20" s="1"/>
       <c r="N20" s="1"/>
       <c r="O20" s="1"/>
-      <c r="P20" s="1"/>
-      <c r="Q20" s="8"/>
+      <c r="P20" s="8"/>
+      <c r="Q20" s="1"/>
       <c r="R20" s="1"/>
       <c r="S20" s="1"/>
       <c r="T20" s="1"/>
       <c r="U20" s="1"/>
       <c r="V20" s="1"/>
-      <c r="W20" s="1"/>
+      <c r="W20" s="11"/>
       <c r="X20" s="11"/>
       <c r="Y20" s="11"/>
-      <c r="Z20" s="11"/>
+      <c r="Z20" s="1"/>
       <c r="AA20" s="1"/>
       <c r="AB20" s="1"/>
       <c r="AC20" s="1"/>
@@ -1554,29 +1424,19 @@
       <c r="AF20" s="1"/>
       <c r="AG20" s="1"/>
       <c r="AH20" s="1"/>
-      <c r="AI20" s="1"/>
+      <c r="AI20" s="11"/>
       <c r="AJ20" s="11"/>
       <c r="AK20" s="11"/>
-      <c r="AL20" s="11"/>
+      <c r="AL20" s="1"/>
       <c r="AM20" s="1"/>
       <c r="AN20" s="1"/>
       <c r="AO20" s="1"/>
       <c r="AP20" s="1"/>
       <c r="AQ20" s="1"/>
       <c r="AR20" s="1"/>
-      <c r="AS20" s="1"/>
-      <c r="AT20" s="1"/>
-      <c r="AU20" s="1"/>
-      <c r="AV20" s="1"/>
-      <c r="AW20" s="1"/>
-      <c r="AX20" s="1"/>
-      <c r="AY20" s="1"/>
-      <c r="AZ20" s="1"/>
-      <c r="BA20" s="1"/>
-      <c r="BB20" s="1"/>
-      <c r="BC20" s="5"/>
-    </row>
-    <row r="21" spans="4:55" ht="33.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="AS20" s="5"/>
+    </row>
+    <row r="21" spans="4:45" ht="33.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="D21" s="1"/>
       <c r="E21" s="3"/>
       <c r="F21" s="1"/>
@@ -1589,65 +1449,55 @@
       <c r="M21" s="1"/>
       <c r="N21" s="1"/>
       <c r="O21" s="1"/>
-      <c r="P21" s="1"/>
-      <c r="Q21" s="8"/>
+      <c r="P21" s="8"/>
+      <c r="Q21" s="1"/>
       <c r="R21" s="1"/>
       <c r="S21" s="1"/>
       <c r="T21" s="1"/>
       <c r="U21" s="1"/>
-      <c r="V21" s="1"/>
+      <c r="V21" s="11"/>
       <c r="W21" s="11"/>
       <c r="X21" s="11"/>
       <c r="Y21" s="11"/>
       <c r="Z21" s="11"/>
-      <c r="AA21" s="11"/>
+      <c r="AA21" s="1"/>
       <c r="AB21" s="1"/>
       <c r="AC21" s="1"/>
       <c r="AD21" s="1"/>
       <c r="AE21" s="1"/>
       <c r="AF21" s="1"/>
       <c r="AG21" s="1"/>
-      <c r="AH21" s="1"/>
+      <c r="AH21" s="11"/>
       <c r="AI21" s="11"/>
       <c r="AJ21" s="11"/>
       <c r="AK21" s="11"/>
       <c r="AL21" s="11"/>
-      <c r="AM21" s="11"/>
+      <c r="AM21" s="1"/>
       <c r="AN21" s="1"/>
       <c r="AO21" s="1"/>
       <c r="AP21" s="1"/>
       <c r="AQ21" s="1"/>
       <c r="AR21" s="1"/>
-      <c r="AS21" s="1"/>
-      <c r="AT21" s="1"/>
-      <c r="AU21" s="1"/>
-      <c r="AV21" s="1"/>
-      <c r="AW21" s="1"/>
-      <c r="AX21" s="1"/>
-      <c r="AY21" s="1"/>
-      <c r="AZ21" s="1"/>
-      <c r="BA21" s="1"/>
-      <c r="BB21" s="1"/>
-      <c r="BC21" s="5"/>
-    </row>
-    <row r="22" spans="4:55" ht="33.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AS21" s="5"/>
+    </row>
+    <row r="22" spans="4:45" ht="33.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D22" s="2"/>
       <c r="E22" s="2"/>
       <c r="F22" s="2"/>
       <c r="G22" s="2"/>
       <c r="H22" s="2"/>
       <c r="I22" s="2"/>
-      <c r="J22" s="2"/>
+      <c r="J22" s="7"/>
       <c r="K22" s="7"/>
-      <c r="L22" s="7"/>
+      <c r="L22" s="2"/>
       <c r="M22" s="2"/>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
       <c r="P22" s="2"/>
       <c r="Q22" s="2"/>
       <c r="R22" s="2"/>
-      <c r="S22" s="2"/>
-      <c r="T22" s="7"/>
+      <c r="S22" s="7"/>
+      <c r="T22" s="2"/>
       <c r="U22" s="2"/>
       <c r="V22" s="2"/>
       <c r="W22" s="2"/>
@@ -1658,8 +1508,8 @@
       <c r="AB22" s="2"/>
       <c r="AC22" s="2"/>
       <c r="AD22" s="2"/>
-      <c r="AE22" s="2"/>
-      <c r="AF22" s="7"/>
+      <c r="AE22" s="7"/>
+      <c r="AF22" s="2"/>
       <c r="AG22" s="2"/>
       <c r="AH22" s="2"/>
       <c r="AI22" s="2"/>
@@ -1673,35 +1523,25 @@
       <c r="AQ22" s="2"/>
       <c r="AR22" s="2"/>
       <c r="AS22" s="2"/>
-      <c r="AT22" s="2"/>
-      <c r="AU22" s="2"/>
-      <c r="AV22" s="2"/>
-      <c r="AW22" s="2"/>
-      <c r="AX22" s="2"/>
-      <c r="AY22" s="2"/>
-      <c r="AZ22" s="2"/>
-      <c r="BA22" s="2"/>
-      <c r="BB22" s="2"/>
-      <c r="BC22" s="2"/>
-    </row>
-    <row r="23" spans="4:55" ht="33.5" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="23" spans="4:45" ht="33.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D23" s="2"/>
       <c r="E23" s="2"/>
       <c r="F23" s="2"/>
       <c r="G23" s="2"/>
       <c r="H23" s="2"/>
       <c r="I23" s="2"/>
-      <c r="J23" s="2"/>
+      <c r="J23" s="4"/>
       <c r="K23" s="4"/>
-      <c r="L23" s="4"/>
+      <c r="L23" s="2"/>
       <c r="M23" s="2"/>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
       <c r="P23" s="2"/>
       <c r="Q23" s="2"/>
       <c r="R23" s="2"/>
-      <c r="S23" s="2"/>
-      <c r="T23" s="4"/>
+      <c r="S23" s="4"/>
+      <c r="T23" s="2"/>
       <c r="U23" s="2"/>
       <c r="V23" s="2"/>
       <c r="W23" s="2"/>
@@ -1712,8 +1552,8 @@
       <c r="AB23" s="2"/>
       <c r="AC23" s="2"/>
       <c r="AD23" s="2"/>
-      <c r="AE23" s="2"/>
-      <c r="AF23" s="4"/>
+      <c r="AE23" s="4"/>
+      <c r="AF23" s="2"/>
       <c r="AG23" s="2"/>
       <c r="AH23" s="2"/>
       <c r="AI23" s="2"/>
@@ -1727,18 +1567,8 @@
       <c r="AQ23" s="2"/>
       <c r="AR23" s="2"/>
       <c r="AS23" s="2"/>
-      <c r="AT23" s="2"/>
-      <c r="AU23" s="2"/>
-      <c r="AV23" s="2"/>
-      <c r="AW23" s="2"/>
-      <c r="AX23" s="2"/>
-      <c r="AY23" s="2"/>
-      <c r="AZ23" s="2"/>
-      <c r="BA23" s="2"/>
-      <c r="BB23" s="2"/>
-      <c r="BC23" s="2"/>
-    </row>
-    <row r="24" spans="4:55" ht="33.5" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="24" spans="4:45" ht="33.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D24" s="2"/>
       <c r="E24" s="2"/>
       <c r="F24" s="2"/>
@@ -1781,25 +1611,58 @@
       <c r="AQ24" s="2"/>
       <c r="AR24" s="2"/>
       <c r="AS24" s="2"/>
-      <c r="AT24" s="2"/>
-      <c r="AU24" s="2"/>
-      <c r="AV24" s="2"/>
-      <c r="AW24" s="2"/>
-      <c r="AX24" s="2"/>
-      <c r="AY24" s="2"/>
-      <c r="AZ24" s="2"/>
-      <c r="BA24" s="2"/>
-      <c r="BB24" s="2"/>
-      <c r="BC24" s="2"/>
-    </row>
-    <row r="25" spans="4:55" ht="33.5" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="26" spans="4:55" ht="33.5" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="27" spans="4:55" ht="33.5" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="28" spans="4:55" ht="33.5" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="29" spans="4:55" ht="33.5" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="30" spans="4:55" ht="33.5" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="31" spans="4:55" ht="33.5" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="32" spans="4:55" ht="33.5" customHeight="1" x14ac:dyDescent="0.3"/>
+    </row>
+    <row r="25" spans="4:45" ht="33.5" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="26" spans="4:45" ht="33.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D26" s="1"/>
+      <c r="E26" s="1"/>
+      <c r="F26" s="1"/>
+      <c r="G26" s="1"/>
+      <c r="H26" s="1"/>
+      <c r="I26" s="1"/>
+      <c r="J26" s="1"/>
+      <c r="K26" s="1"/>
+      <c r="L26" s="1"/>
+      <c r="M26" s="1"/>
+      <c r="N26" s="1"/>
+      <c r="O26" s="1"/>
+      <c r="P26" s="1"/>
+      <c r="Q26" s="1"/>
+      <c r="R26" s="1"/>
+      <c r="S26" s="1"/>
+      <c r="T26" s="1"/>
+      <c r="U26" s="1"/>
+      <c r="V26" s="1"/>
+      <c r="W26" s="1"/>
+      <c r="X26" s="1"/>
+      <c r="Y26" s="1"/>
+      <c r="Z26" s="1"/>
+      <c r="AA26" s="1"/>
+      <c r="AB26" s="1"/>
+      <c r="AC26" s="1"/>
+      <c r="AD26" s="1"/>
+      <c r="AE26" s="1"/>
+      <c r="AF26" s="1"/>
+      <c r="AG26" s="1"/>
+      <c r="AH26" s="1"/>
+      <c r="AI26" s="1"/>
+      <c r="AJ26" s="1"/>
+      <c r="AK26" s="1"/>
+      <c r="AL26" s="1"/>
+      <c r="AM26" s="1"/>
+      <c r="AN26" s="1"/>
+      <c r="AO26" s="1"/>
+      <c r="AP26" s="1"/>
+      <c r="AQ26" s="1"/>
+      <c r="AR26" s="1"/>
+      <c r="AS26" s="1"/>
+    </row>
+    <row r="27" spans="4:45" ht="33.5" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="28" spans="4:45" ht="33.5" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="29" spans="4:45" ht="33.5" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="30" spans="4:45" ht="33.5" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="31" spans="4:45" ht="33.5" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="32" spans="4:45" ht="33.5" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="33" ht="33.5" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="34" ht="33.5" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="35" ht="33.5" customHeight="1" x14ac:dyDescent="0.3"/>
